--- a/diseases/d059/2026-2029.xlsx
+++ b/diseases/d059/2026-2029.xlsx
@@ -25701,12 +25701,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -25731,12 +25731,12 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N149" t="n">
@@ -25779,40 +25779,185 @@
       </c>
       <c r="AV149" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA149" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC149" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr"/>
+      <c r="AT150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW149" t="inlineStr">
+      <c r="AW150" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX149" t="inlineStr">
+      <c r="AX150" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY149" t="inlineStr">
+      <c r="AY150" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ149" t="inlineStr">
+      <c r="AZ150" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA149" t="inlineStr">
+      <c r="BA150" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB149" t="inlineStr">
+      <c r="BB150" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC149" t="inlineStr">
+      <c r="BC150" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -25934,7 +26079,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10">
@@ -25944,7 +26089,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d059/2026-2029.xlsx
+++ b/diseases/d059/2026-2029.xlsx
@@ -25846,118 +25846,512 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="AT150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>Yellow Fever</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN151" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP151" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="AT151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV151" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA151" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
+      <c r="G152" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>D059</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>Yellow fever</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
         <is>
           <t>黄热病</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
+      <c r="K152" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr">
+      <c r="L152" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M150" t="inlineStr">
+      <c r="M152" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N150" t="n">
-        <v>0</v>
-      </c>
-      <c r="O150" t="n">
-        <v>0</v>
-      </c>
-      <c r="R150" t="n">
-        <v>0</v>
-      </c>
-      <c r="S150" t="inlineStr">
+      <c r="N152" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="R152" t="n">
+        <v>0</v>
+      </c>
+      <c r="S152" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO150" t="inlineStr">
+      <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP150" t="inlineStr">
+      <c r="AP152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR150" t="inlineStr">
+      <c r="AR152" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS150" t="inlineStr"/>
-      <c r="AT150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU150" t="inlineStr">
+      <c r="AS152" t="inlineStr"/>
+      <c r="AT152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU152" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV150" t="inlineStr">
+      <c r="AV152" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW150" t="inlineStr">
+      <c r="AW152" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX150" t="inlineStr">
+      <c r="AX152" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY150" t="inlineStr">
+      <c r="AY152" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ150" t="inlineStr">
+      <c r="AZ152" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA150" t="inlineStr">
+      <c r="BA152" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB150" t="inlineStr">
+      <c r="BB152" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC150" t="inlineStr">
+      <c r="BC152" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -26079,7 +26473,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10">
@@ -26089,7 +26483,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11">
@@ -26109,7 +26503,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d059/2026-2029.xlsx
+++ b/diseases/d059/2026-2029.xlsx
@@ -26357,6 +26357,151 @@
         </is>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr"/>
+      <c r="AT153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA153" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26390,7 +26535,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -26473,7 +26618,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10">
@@ -26483,7 +26628,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d059/2026-2029.xlsx
+++ b/diseases/d059/2026-2029.xlsx
@@ -26502,6 +26502,400 @@
         </is>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="AT154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV154" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA154" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB154" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC154" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>Yellow Fever</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN155" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP155" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="AT155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26618,7 +27012,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10">
@@ -26628,7 +27022,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
@@ -26648,7 +27042,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d059/2026-2029.xlsx
+++ b/diseases/d059/2026-2029.xlsx
@@ -23400,12 +23400,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -23478,42 +23478,42 @@
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -23545,12 +23545,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -23575,7 +23575,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -23623,42 +23623,42 @@
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -23690,12 +23690,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -23734,9 +23734,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="P138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
@@ -23745,77 +23742,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA138" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ138" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS138" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23842,7 +23830,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -23894,98 +23882,18 @@
       <c r="P139" t="n">
         <v>0</v>
       </c>
-      <c r="U139" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER</t>
-        </is>
-      </c>
-      <c r="V139" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER</t>
-        </is>
-      </c>
-      <c r="W139" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X139" t="inlineStr">
-        <is>
-          <t>Yellow Fever</t>
-        </is>
-      </c>
-      <c r="Y139" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD139" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE139" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF139" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG139" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ139" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN139" t="b">
-        <v>1</v>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
@@ -24079,17 +23987,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -24114,7 +24022,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -24128,76 +24036,168 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="R140" t="n">
-        <v>0</v>
-      </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>Yellow Fever</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN140" t="b">
+        <v>1</v>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
       <c r="AT140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -24229,12 +24229,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -24273,9 +24273,6 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
-      <c r="P141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
@@ -24284,77 +24281,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA141" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ141" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24381,7 +24369,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -24433,98 +24421,18 @@
       <c r="P142" t="n">
         <v>0</v>
       </c>
-      <c r="U142" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER</t>
-        </is>
-      </c>
-      <c r="V142" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER</t>
-        </is>
-      </c>
-      <c r="W142" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X142" t="inlineStr">
-        <is>
-          <t>Yellow Fever</t>
-        </is>
-      </c>
-      <c r="Y142" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD142" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE142" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF142" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG142" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH142" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ142" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK142" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN142" t="b">
-        <v>1</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
@@ -24618,17 +24526,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24653,7 +24561,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -24667,76 +24575,168 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="R143" t="n">
-        <v>0</v>
-      </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>Yellow Fever</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN143" t="b">
+        <v>1</v>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
       <c r="AT143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -24768,12 +24768,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24812,9 +24812,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="P144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -24823,77 +24820,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA144" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ144" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24920,7 +24908,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -24972,98 +24960,18 @@
       <c r="P145" t="n">
         <v>0</v>
       </c>
-      <c r="U145" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER</t>
-        </is>
-      </c>
-      <c r="V145" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER</t>
-        </is>
-      </c>
-      <c r="W145" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X145" t="inlineStr">
-        <is>
-          <t>Yellow Fever</t>
-        </is>
-      </c>
-      <c r="Y145" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R145" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD145" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE145" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF145" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG145" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH145" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI145" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM145" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN145" t="b">
-        <v>1</v>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
@@ -25157,17 +25065,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -25192,7 +25100,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -25206,76 +25114,168 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="R146" t="n">
-        <v>0</v>
-      </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>Yellow Fever</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM146" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN146" t="b">
+        <v>1</v>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS146" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
       <c r="AT146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -25307,12 +25307,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -25351,9 +25351,6 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
-      <c r="P147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
@@ -25362,77 +25359,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA147" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ147" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS147" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25459,7 +25447,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -25511,98 +25499,18 @@
       <c r="P148" t="n">
         <v>0</v>
       </c>
-      <c r="U148" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER</t>
-        </is>
-      </c>
-      <c r="V148" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER</t>
-        </is>
-      </c>
-      <c r="W148" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X148" t="inlineStr">
-        <is>
-          <t>Yellow Fever</t>
-        </is>
-      </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R148" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD148" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE148" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF148" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG148" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH148" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI148" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ148" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK148" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM148" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN148" t="b">
-        <v>1</v>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
@@ -25696,17 +25604,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -25731,7 +25639,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -25745,76 +25653,168 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
-      <c r="R149" t="n">
-        <v>0</v>
-      </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P149" t="n">
+        <v>0</v>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>Yellow Fever</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN149" t="b">
+        <v>1</v>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS149" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
       <c r="AT149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -25846,12 +25846,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -25890,9 +25890,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="P150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -25901,77 +25898,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA150" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ150" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS150" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25998,7 +25986,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -26050,98 +26038,18 @@
       <c r="P151" t="n">
         <v>0</v>
       </c>
-      <c r="U151" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER</t>
-        </is>
-      </c>
-      <c r="V151" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER</t>
-        </is>
-      </c>
-      <c r="W151" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>Yellow Fever</t>
-        </is>
-      </c>
-      <c r="Y151" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R151" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD151" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE151" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF151" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG151" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH151" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI151" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK151" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN151" t="b">
-        <v>1</v>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
@@ -26235,17 +26143,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -26270,12 +26178,12 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N152" t="n">
@@ -26284,76 +26192,168 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="R152" t="n">
-        <v>0</v>
-      </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>Yellow Fever</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN152" t="b">
+        <v>1</v>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
       <c r="AT152" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -26385,12 +26385,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -26415,7 +26415,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -26463,42 +26463,42 @@
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -26530,12 +26530,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -26574,9 +26574,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="P154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -26585,77 +26582,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA154" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ154" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS154" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26682,7 +26670,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -26734,98 +26722,18 @@
       <c r="P155" t="n">
         <v>0</v>
       </c>
-      <c r="U155" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER</t>
-        </is>
-      </c>
-      <c r="V155" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER</t>
-        </is>
-      </c>
-      <c r="W155" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X155" t="inlineStr">
-        <is>
-          <t>Yellow Fever</t>
-        </is>
-      </c>
-      <c r="Y155" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R155" t="n">
+        <v>0</v>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD155" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE155" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF155" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG155" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ155" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK155" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM155" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN155" t="b">
-        <v>1</v>
       </c>
       <c r="AO155" t="inlineStr">
         <is>
@@ -26891,6 +26799,782 @@
         </is>
       </c>
       <c r="BC155" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>Yellow Fever</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN156" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP156" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="AT156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV156" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA156" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB156" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC156" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP157" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr"/>
+      <c r="AT157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV157" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA157" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB157" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC157" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="AT158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV158" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA158" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB158" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC158" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>0</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="n">
+        <v>0</v>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>Yellow Fever</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN159" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="AT159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV159" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA159" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB159" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC159" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -26929,7 +27613,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -27012,7 +27696,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10">
@@ -27022,7 +27706,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11">
@@ -27042,7 +27726,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d059/2026-2029.xlsx
+++ b/diseases/d059/2026-2029.xlsx
@@ -27580,6 +27580,690 @@
         </is>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP160" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr"/>
+      <c r="AT160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV160" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA160" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB160" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC160" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="AT161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV161" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA161" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB161" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC161" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>Yellow Fever</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN162" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="AT162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA162" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB162" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC162" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr"/>
+      <c r="AT163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27613,7 +28297,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -27696,7 +28380,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10">
@@ -27706,7 +28390,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -27726,7 +28410,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d059/2026-2029.xlsx
+++ b/diseases/d059/2026-2029.xlsx
@@ -28147,12 +28147,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -28177,12 +28177,12 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N163" t="n">
@@ -28225,40 +28225,185 @@
       </c>
       <c r="AV163" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr"/>
+      <c r="AT164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW163" t="inlineStr">
+      <c r="AW164" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX163" t="inlineStr">
+      <c r="AX164" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY163" t="inlineStr">
+      <c r="AY164" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ163" t="inlineStr">
+      <c r="AZ164" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA163" t="inlineStr">
+      <c r="BA164" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB163" t="inlineStr">
+      <c r="BB164" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC163" t="inlineStr">
+      <c r="BC164" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -28380,7 +28525,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10">
@@ -28390,7 +28535,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d059/2026-2029.xlsx
+++ b/diseases/d059/2026-2029.xlsx
@@ -773,6 +773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -918,6 +923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1756,6 +1771,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2446,6 +2466,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3136,6 +3161,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3826,6 +3856,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3971,6 +4006,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4116,6 +4156,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4806,6 +4851,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5496,6 +5546,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6186,6 +6241,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6876,6 +6936,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7021,6 +7086,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7166,6 +7236,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7856,6 +7931,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8546,6 +8626,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9236,6 +9321,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9926,6 +10016,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10465,6 +10560,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10610,6 +10710,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10906,6 +11011,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11596,6 +11706,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12286,6 +12401,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12976,6 +13096,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13515,6 +13640,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13660,6 +13790,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13956,6 +14091,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14646,6 +14786,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15336,6 +15481,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16026,6 +16176,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16716,6 +16871,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17255,6 +17415,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17400,6 +17565,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17690,6 +17860,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18374,6 +18549,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19058,6 +19238,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19742,6 +19927,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20281,6 +20471,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20426,6 +20621,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20716,6 +20916,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21400,6 +21605,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22084,6 +22294,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22768,6 +22983,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23452,6 +23672,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23597,6 +23822,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26437,6 +26667,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28292,118 +28527,517 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="AT164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA164" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" t="n">
+        <v>0</v>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>Yellow Fever</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN165" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="AT165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr">
+      <c r="G166" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>D059</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Yellow fever</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
         <is>
           <t>黄热病</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
+      <c r="K166" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr">
+      <c r="L166" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M164" t="inlineStr">
+      <c r="M166" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N164" t="n">
-        <v>0</v>
-      </c>
-      <c r="O164" t="n">
-        <v>0</v>
-      </c>
-      <c r="R164" t="n">
-        <v>0</v>
-      </c>
-      <c r="S164" t="inlineStr">
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO164" t="inlineStr">
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP164" t="inlineStr">
+      <c r="AP166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR164" t="inlineStr">
+      <c r="AR166" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS164" t="inlineStr"/>
-      <c r="AT164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU164" t="inlineStr">
+      <c r="AS166" t="inlineStr"/>
+      <c r="AT166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU166" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV164" t="inlineStr">
+      <c r="AV166" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW164" t="inlineStr">
+      <c r="AW166" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX164" t="inlineStr">
+      <c r="AX166" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY164" t="inlineStr">
+      <c r="AY166" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ164" t="inlineStr">
+      <c r="AZ166" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA164" t="inlineStr">
+      <c r="BA166" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB164" t="inlineStr">
+      <c r="BB166" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC164" t="inlineStr">
+      <c r="BC166" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -28525,7 +29159,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10">
@@ -28535,7 +29169,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -28555,7 +29189,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d059/2026-2029.xlsx
+++ b/diseases/d059/2026-2029.xlsx
@@ -29043,6 +29043,151 @@
         </is>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0</v>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr"/>
+      <c r="AT167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29076,7 +29221,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -29159,7 +29304,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10">
@@ -29169,7 +29314,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d059/2026-2029.xlsx
+++ b/diseases/d059/2026-2029.xlsx
@@ -29188,6 +29188,400 @@
         </is>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="AT168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>Yellow Fever</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN169" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="AT169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV169" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA169" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB169" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC169" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29304,7 +29698,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10">
@@ -29314,7 +29708,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">
@@ -29334,7 +29728,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
